--- a/data/trans_dic/P56$auxiliar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 23,15</t>
+          <t>6,08; 22,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,03</t>
+          <t>2,85; 17,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 35,09</t>
+          <t>18,37; 35,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 16,07</t>
+          <t>2,78; 15,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,68; 29,13</t>
+          <t>16,58; 28,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 14,15</t>
+          <t>3,67; 13,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,31; 31,93</t>
+          <t>23,75; 32,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,11</t>
+          <t>1,82; 10,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 25,41</t>
+          <t>14,31; 24,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,8</t>
+          <t>4,22; 12,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 31,49</t>
+          <t>23,38; 31,45</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 28,66</t>
+          <t>6,45; 27,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,74</t>
+          <t>0,0; 25,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 39,2</t>
+          <t>19,68; 39,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,26</t>
+          <t>0,0; 16,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 31,87</t>
+          <t>16,76; 31,78</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,55</t>
+          <t>0,0; 44,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,06</t>
+          <t>0,0; 23,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 20,49</t>
+          <t>5,47; 20,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,61</t>
+          <t>2,24; 13,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 28,53</t>
+          <t>15,88; 28,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,79</t>
+          <t>2,34; 13,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 26,33</t>
+          <t>15,17; 27,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,62</t>
+          <t>3,08; 11,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,0; 31,74</t>
+          <t>23,66; 31,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,64; 10,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 23,02</t>
+          <t>12,96; 22,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,07</t>
+          <t>3,68; 10,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,91; 30,1</t>
+          <t>22,84; 29,64</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1722</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4115; 15832</t>
+          <t>4160; 15652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1630; 9088</t>
+          <t>1617; 9648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12171; 23830</t>
+          <t>12475; 24190</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2566; 13406</t>
+          <t>2318; 12993</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31010; 54163</t>
+          <t>30826; 53179</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5049; 20196</t>
+          <t>5239; 19547</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46749; 64042</t>
+          <t>47637; 64939</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2221; 12895</t>
+          <t>2316; 13826</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38000; 64617</t>
+          <t>36405; 62887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8048; 23540</t>
+          <t>8420; 25450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63593; 84538</t>
+          <t>62777; 84437</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1268</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1622</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2033; 7766</t>
+          <t>1749; 7556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1788</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1845</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5264</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8413; 16492</t>
+          <t>8282; 16507</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1712</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5215</t>
+          <t>0; 6196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11928; 22044</t>
+          <t>11592; 21984</t>
         </is>
       </c>
     </row>
@@ -1925,57 +1925,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2882</t>
+          <t>0; 2862</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>0; 3078</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4144; 16088</t>
+          <t>4292; 16169</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1641; 9814</t>
+          <t>1616; 9403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15817; 28950</t>
+          <t>16112; 28971</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2942; 12902</t>
+          <t>2188; 12254</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29952; 53229</t>
+          <t>30660; 55077</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6053; 21681</t>
+          <t>5291; 20263</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59789; 79076</t>
+          <t>58929; 79200</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2256; 12751</t>
+          <t>2331; 14510</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38392; 64598</t>
+          <t>36361; 63752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8909; 24568</t>
+          <t>8984; 25963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80325; 105544</t>
+          <t>80059; 103923</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$auxiliar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 22,88</t>
+          <t>6,23; 22,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 17,02</t>
+          <t>2,89; 16,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 35,62</t>
+          <t>17,63; 35,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 15,58</t>
+          <t>2,5; 14,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 28,6</t>
+          <t>16,32; 28,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,7</t>
+          <t>3,39; 14,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,38</t>
+          <t>23,71; 32,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,84</t>
+          <t>1,84; 10,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 24,73</t>
+          <t>15,03; 25,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 12,76</t>
+          <t>3,83; 11,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,38; 31,45</t>
+          <t>23,6; 31,46</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 27,88</t>
+          <t>7,21; 28,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,33</t>
+          <t>0,0; 20,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 39,23</t>
+          <t>20,9; 39,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,95</t>
+          <t>0,0; 16,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 31,78</t>
+          <t>18,17; 32,4</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,25</t>
+          <t>0,0; 41,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,78</t>
+          <t>0,0; 24,62</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 20,6</t>
+          <t>4,85; 20,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,04</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 28,55</t>
+          <t>15,63; 28,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,1</t>
+          <t>2,41; 13,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,17; 27,25</t>
+          <t>15,11; 26,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,8</t>
+          <t>3,06; 12,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,66; 31,79</t>
+          <t>23,98; 31,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,23</t>
+          <t>1,62; 9,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 22,72</t>
+          <t>13,61; 22,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,65</t>
+          <t>3,67; 10,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,84; 29,64</t>
+          <t>22,49; 29,2</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55919</t>
+          <t>60196</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73738</t>
+          <t>79194</t>
         </is>
       </c>
     </row>
@@ -1509,57 +1509,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4160; 15652</t>
+          <t>4259; 15096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1617; 9648</t>
+          <t>1636; 9515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12475; 24190</t>
+          <t>12737; 25672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2318; 12993</t>
+          <t>2083; 12155</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30826; 53179</t>
+          <t>30344; 53750</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5239; 19547</t>
+          <t>4841; 20064</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47637; 64939</t>
+          <t>51495; 70699</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2316; 13826</t>
+          <t>2353; 13001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36405; 62887</t>
+          <t>38236; 64798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8420; 25450</t>
+          <t>7643; 22826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62777; 84437</t>
+          <t>68307; 91040</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>18516</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1749; 7556</t>
+          <t>2060; 8193</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6430</t>
+          <t>0; 5196</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8282; 16507</t>
+          <t>10043; 19017</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6196</t>
+          <t>0; 5975</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11592; 21984</t>
+          <t>13926; 24839</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1065</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2862</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 3770</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>98775</t>
         </is>
       </c>
     </row>
@@ -2133,57 +2133,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4292; 16169</t>
+          <t>3809; 15906</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1616; 9403</t>
+          <t>1575; 9401</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16112; 28971</t>
+          <t>16881; 30690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2188; 12254</t>
+          <t>2251; 12977</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30660; 55077</t>
+          <t>30536; 53720</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5291; 20263</t>
+          <t>5260; 20992</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58929; 79200</t>
+          <t>65561; 86489</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2331; 14510</t>
+          <t>2297; 13806</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36361; 63752</t>
+          <t>38200; 62900</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8984; 25963</t>
+          <t>8941; 25086</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80059; 103923</t>
+          <t>85785; 111380</t>
         </is>
       </c>
     </row>
